--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,67</t>
+          <t>0,58; 2,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,49</t>
+          <t>0,41; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,45</t>
+          <t>1,36; 4,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,01</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,86</t>
+          <t>1,17; 3,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,27</t>
+          <t>0,69; 3,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,49</t>
+          <t>2,3; 6,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,83</t>
+          <t>0,69; 6,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,79</t>
+          <t>1,08; 2,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,39</t>
+          <t>0,76; 2,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,66</t>
+          <t>2,21; 4,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,4</t>
+          <t>0,74; 4,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,43</t>
+          <t>1,3; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,43</t>
+          <t>0,68; 2,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,96</t>
+          <t>1,31; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,05</t>
+          <t>0,9; 4,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,56</t>
+          <t>1,16; 3,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,85</t>
+          <t>1,88; 4,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,26</t>
+          <t>2,12; 5,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,15</t>
+          <t>1,38; 4,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,98</t>
+          <t>1,45; 3,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,08</t>
+          <t>1,47; 3,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,88</t>
+          <t>1,99; 4,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,18</t>
+          <t>1,59; 4,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,13</t>
+          <t>2,07; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,54</t>
+          <t>3,15; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,36</t>
+          <t>2,45; 5,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,61</t>
+          <t>2,03; 5,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,82</t>
+          <t>3,26; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,68</t>
+          <t>3,28; 6,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,92</t>
+          <t>6,12; 10,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,97</t>
+          <t>1,73; 4,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,31</t>
+          <t>2,98; 5,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,22</t>
+          <t>3,59; 5,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,14</t>
+          <t>4,79; 7,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,08</t>
+          <t>2,09; 4,15</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,81</t>
+          <t>1,19; 4,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,05</t>
+          <t>1,75; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,32</t>
+          <t>3,76; 7,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,42</t>
+          <t>1,21; 5,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,74</t>
+          <t>3,71; 7,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,55</t>
+          <t>3,75; 7,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 15,23</t>
+          <t>9,7; 15,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,46</t>
+          <t>3,76; 6,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,23</t>
+          <t>2,77; 5,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,63</t>
+          <t>3,08; 5,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 10,47</t>
+          <t>7,2; 10,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,29</t>
+          <t>2,54; 5,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,58</t>
+          <t>2,35; 6,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,14</t>
+          <t>1,83; 5,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,0</t>
+          <t>4,88; 10,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,79</t>
+          <t>2,63; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,13</t>
+          <t>3,7; 8,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,03</t>
+          <t>3,76; 8,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,48</t>
+          <t>15,28; 22,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,98</t>
+          <t>4,99; 7,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,42</t>
+          <t>3,58; 6,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,03</t>
+          <t>3,29; 6,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,22</t>
+          <t>10,92; 15,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,28</t>
+          <t>4,13; 6,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,91</t>
+          <t>2,39; 6,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,13</t>
+          <t>2,47; 7,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,84</t>
+          <t>2,34; 6,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,07</t>
+          <t>2,06; 5,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,25</t>
+          <t>4,62; 10,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,69</t>
+          <t>6,65; 12,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,81; 20,5</t>
+          <t>12,64; 20,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 73,87</t>
+          <t>5,8; 71,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,69</t>
+          <t>4,12; 7,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,2</t>
+          <t>5,32; 9,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,3</t>
+          <t>8,41; 13,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 58,93</t>
+          <t>4,56; 59,26</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,89</t>
+          <t>1,66; 6,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,61</t>
+          <t>2,55; 8,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,23</t>
+          <t>5,76; 12,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,86</t>
+          <t>3,08; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,46</t>
+          <t>4,52; 10,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,18</t>
+          <t>3,97; 8,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,12; 21,48</t>
+          <t>12,98; 21,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,53</t>
+          <t>4,32; 7,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,83</t>
+          <t>4,02; 8,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,88</t>
+          <t>4,16; 8,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 16,75</t>
+          <t>10,86; 16,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,83</t>
+          <t>4,17; 6,74</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,4</t>
+          <t>2,25; 3,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,66</t>
+          <t>2,55; 3,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,28</t>
+          <t>3,81; 5,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,1</t>
+          <t>2,39; 3,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,36</t>
+          <t>3,93; 5,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 5,83</t>
+          <t>4,23; 5,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,16</t>
+          <t>9,92; 12,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 26,62</t>
+          <t>4,35; 26,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,19</t>
+          <t>3,27; 4,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,51</t>
+          <t>3,59; 4,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,52</t>
+          <t>7,25; 8,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 16,58</t>
+          <t>3,78; 15,79</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2813; 13201</t>
+          <t>2861; 13219</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2012; 11288</t>
+          <t>1842; 10545</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5471; 18659</t>
+          <t>5706; 18997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 20024</t>
+          <t>0; 22053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5521; 18036</t>
+          <t>5482; 17369</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3031; 14048</t>
+          <t>2949; 14010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9669; 25670</t>
+          <t>9093; 25933</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1868; 18271</t>
+          <t>2172; 19340</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10637; 26865</t>
+          <t>10373; 26049</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6719; 21174</t>
+          <t>6754; 20660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18084; 38016</t>
+          <t>18049; 38706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5462; 31391</t>
+          <t>5275; 31614</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8930; 25231</t>
+          <t>9574; 23890</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4591; 16707</t>
+          <t>4642; 16402</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7832; 23379</t>
+          <t>7714; 22091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3984; 21397</t>
+          <t>3807; 20176</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7361; 22285</t>
+          <t>7276; 22778</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11373; 29598</t>
+          <t>11469; 29113</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12866; 29646</t>
+          <t>11972; 29147</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7333; 26363</t>
+          <t>7045; 24627</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18764; 40507</t>
+          <t>19746; 41800</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19665; 39974</t>
+          <t>19130; 39986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23297; 44722</t>
+          <t>22925; 46468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14736; 39091</t>
+          <t>14882; 39695</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13154; 32756</t>
+          <t>13225; 34079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20551; 44608</t>
+          <t>21464; 45176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16259; 35853</t>
+          <t>16410; 36893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11177; 30070</t>
+          <t>10862; 29873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21807; 47037</t>
+          <t>22503; 46828</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23530; 47516</t>
+          <t>23348; 48279</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39268; 65628</t>
+          <t>40489; 67109</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10218; 23527</t>
+          <t>10259; 24709</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39715; 70512</t>
+          <t>39584; 71560</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50519; 86584</t>
+          <t>49997; 83413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61981; 95022</t>
+          <t>63756; 94382</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24314; 46024</t>
+          <t>23556; 46785</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6158; 19784</t>
+          <t>6200; 20751</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10529; 31030</t>
+          <t>10782; 30751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24215; 47319</t>
+          <t>24280; 46818</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11131; 48126</t>
+          <t>10751; 45442</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18806; 39899</t>
+          <t>19156; 40267</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23197; 46554</t>
+          <t>23098; 45537</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62751; 98864</t>
+          <t>62956; 98694</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26283; 46080</t>
+          <t>26824; 45411</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29478; 54123</t>
+          <t>28617; 53210</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38896; 69336</t>
+          <t>37925; 67593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>94396; 135580</t>
+          <t>93266; 135048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36027; 84679</t>
+          <t>40626; 87255</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9217; 25428</t>
+          <t>9090; 25546</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8294; 22058</t>
+          <t>7877; 22934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23916; 47813</t>
+          <t>23312; 48006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14345; 32470</t>
+          <t>14779; 32624</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14138; 32860</t>
+          <t>14927; 33483</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16225; 35959</t>
+          <t>16855; 36421</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75868; 111710</t>
+          <t>75937; 110922</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27299; 43726</t>
+          <t>27347; 43637</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28152; 50791</t>
+          <t>28307; 52422</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27960; 52859</t>
+          <t>28886; 52835</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105491; 148324</t>
+          <t>106459; 150586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46201; 69708</t>
+          <t>45797; 70744</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7135; 20219</t>
+          <t>7000; 19503</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7732; 22096</t>
+          <t>7660; 22230</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7948; 22880</t>
+          <t>7814; 21953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7225; 18656</t>
+          <t>7585; 19226</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16588; 35141</t>
+          <t>15854; 34535</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24194; 44933</t>
+          <t>23540; 44798</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48395; 77451</t>
+          <t>47758; 77703</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35240; 449430</t>
+          <t>35265; 436522</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26730; 48848</t>
+          <t>26185; 49526</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34939; 61048</t>
+          <t>35336; 60918</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60933; 94680</t>
+          <t>59900; 93227</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44250; 575514</t>
+          <t>44501; 578649</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3639; 14458</t>
+          <t>3478; 13377</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6229; 21512</t>
+          <t>6371; 21665</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15036; 31439</t>
+          <t>14805; 31808</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9330; 22214</t>
+          <t>8722; 20553</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15169; 34926</t>
+          <t>15082; 35349</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16128; 35697</t>
+          <t>15431; 34774</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52519; 85962</t>
+          <t>51957; 86165</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18708; 32059</t>
+          <t>18410; 31900</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21101; 42605</t>
+          <t>21850; 43948</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25675; 50349</t>
+          <t>26557; 52480</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72273; 110080</t>
+          <t>71352; 110684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30504; 48407</t>
+          <t>29568; 47746</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>72645; 111320</t>
+          <t>73626; 110999</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>84953; 125556</t>
+          <t>87233; 129412</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>130162; 179186</t>
+          <t>129217; 177646</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>88845; 141740</t>
+          <t>82858; 137277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>129417; 181201</t>
+          <t>132695; 182661</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>152205; 207429</t>
+          <t>150646; 204182</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>354888; 430916</t>
+          <t>351692; 431385</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>161276; 988032</t>
+          <t>161437; 979354</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>216538; 278899</t>
+          <t>217358; 277457</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>247516; 314833</t>
+          <t>250421; 316364</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>495007; 591483</t>
+          <t>502869; 592778</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>268313; 1189282</t>
+          <t>271451; 1132535</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,68</t>
+          <t>0,59; 2,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,32</t>
+          <t>0,46; 2,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,53</t>
+          <t>1,4; 4,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,72</t>
+          <t>1,18; 3,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,26</t>
+          <t>0,67; 3,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,55</t>
+          <t>2,42; 6,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,17</t>
+          <t>0,61; 5,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,71</t>
+          <t>1,09; 2,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,34</t>
+          <t>0,77; 2,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,75</t>
+          <t>2,21; 4,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,43</t>
+          <t>0,68; 3,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,25</t>
+          <t>1,22; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,39</t>
+          <t>0,67; 2,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,74</t>
+          <t>1,23; 3,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,76</t>
+          <t>1,04; 5,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,64</t>
+          <t>1,15; 3,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,77</t>
+          <t>1,9; 4,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,17</t>
+          <t>2,17; 5,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,81</t>
+          <t>1,96; 6,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,07</t>
+          <t>1,44; 3,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,08</t>
+          <t>1,5; 3,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,03</t>
+          <t>2,12; 3,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,24</t>
+          <t>1,88; 4,75</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,34</t>
+          <t>2,13; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,63</t>
+          <t>3,21; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,51</t>
+          <t>2,5; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,57</t>
+          <t>1,86; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,79</t>
+          <t>3,27; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,79</t>
+          <t>3,23; 6,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,15</t>
+          <t>6,17; 10,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,17</t>
+          <t>1,95; 4,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,39</t>
+          <t>3,04; 5,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,99</t>
+          <t>3,67; 5,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,09</t>
+          <t>4,69; 7,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,15</t>
+          <t>2,23; 4,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,0</t>
+          <t>1,18; 3,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,0</t>
+          <t>1,72; 5,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,25</t>
+          <t>3,78; 7,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,12</t>
+          <t>2,9; 6,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,81</t>
+          <t>3,81; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,39</t>
+          <t>3,78; 7,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 15,21</t>
+          <t>9,84; 15,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,37</t>
+          <t>4,18; 6,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,14</t>
+          <t>2,84; 5,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,49</t>
+          <t>3,1; 5,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,43</t>
+          <t>7,21; 10,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,45</t>
+          <t>3,87; 6,0</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,61</t>
+          <t>2,47; 6,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,34</t>
+          <t>1,87; 5,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,04</t>
+          <t>5,02; 9,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,81</t>
+          <t>2,67; 5,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,29</t>
+          <t>3,61; 8,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,13</t>
+          <t>3,76; 8,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,33</t>
+          <t>15,21; 22,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,96</t>
+          <t>5,17; 8,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,63</t>
+          <t>3,58; 6,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,02</t>
+          <t>3,14; 5,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 15,45</t>
+          <t>11,11; 15,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,38</t>
+          <t>4,25; 6,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,67</t>
+          <t>2,32; 6,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,18</t>
+          <t>2,47; 7,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,57</t>
+          <t>2,39; 6,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,22</t>
+          <t>2,06; 5,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,07</t>
+          <t>4,85; 9,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,65</t>
+          <t>6,61; 12,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 20,57</t>
+          <t>12,65; 20,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 71,75</t>
+          <t>4,89; 8,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,79</t>
+          <t>4,14; 7,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,18</t>
+          <t>5,36; 9,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,09</t>
+          <t>8,22; 13,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 59,26</t>
+          <t>3,95; 6,35</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,37</t>
+          <t>1,65; 6,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,67</t>
+          <t>2,43; 8,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,38</t>
+          <t>5,54; 11,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,27</t>
+          <t>3,59; 8,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,59</t>
+          <t>4,5; 10,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,94</t>
+          <t>4,13; 9,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,98; 21,53</t>
+          <t>13,06; 21,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,49</t>
+          <t>4,29; 7,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,08</t>
+          <t>3,98; 8,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,22</t>
+          <t>4,06; 8,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,86; 16,84</t>
+          <t>10,86; 16,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,74</t>
+          <t>4,4; 6,96</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,39</t>
+          <t>2,26; 3,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,78</t>
+          <t>2,48; 3,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,23</t>
+          <t>3,85; 5,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,97</t>
+          <t>2,88; 4,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,41</t>
+          <t>3,85; 5,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,74</t>
+          <t>4,31; 5,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,17</t>
+          <t>9,96; 12,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,35; 26,38</t>
+          <t>4,22; 5,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,17</t>
+          <t>3,24; 4,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,53</t>
+          <t>3,53; 4,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,54</t>
+          <t>7,22; 8,59</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 15,79</t>
+          <t>3,75; 4,63</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13239</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2861; 13219</t>
+          <t>2931; 14215</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1842; 10545</t>
+          <t>2094; 12198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5706; 18997</t>
+          <t>5870; 19833</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 22053</t>
+          <t>0; 17833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5482; 17369</t>
+          <t>5501; 18087</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2949; 14010</t>
+          <t>2886; 13110</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9093; 25933</t>
+          <t>9563; 25226</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2172; 19340</t>
+          <t>2217; 18911</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10373; 26049</t>
+          <t>10463; 26462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6754; 20660</t>
+          <t>6825; 20924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18049; 38706</t>
+          <t>18006; 37985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5275; 31614</t>
+          <t>5218; 28064</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24581</t>
+          <t>29588</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9574; 23890</t>
+          <t>8960; 23673</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4642; 16402</t>
+          <t>4621; 16614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7714; 22091</t>
+          <t>7235; 22424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3807; 20176</t>
+          <t>4940; 25742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7276; 22778</t>
+          <t>7173; 22871</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11469; 29113</t>
+          <t>11586; 28685</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11972; 29147</t>
+          <t>12209; 30940</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7045; 24627</t>
+          <t>9827; 30337</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19746; 41800</t>
+          <t>19540; 41211</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19130; 39986</t>
+          <t>19451; 40398</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22925; 46468</t>
+          <t>24415; 46000</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14882; 39695</t>
+          <t>18433; 46449</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>38294</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13225; 34079</t>
+          <t>13597; 32909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21464; 45176</t>
+          <t>21920; 46571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16410; 36893</t>
+          <t>16723; 36512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10862; 29873</t>
+          <t>11534; 31544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22503; 46828</t>
+          <t>22556; 46845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23348; 48279</t>
+          <t>22937; 48263</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40489; 67109</t>
+          <t>40776; 66604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10259; 24709</t>
+          <t>12137; 27434</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39584; 71560</t>
+          <t>40336; 71101</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49997; 83413</t>
+          <t>51148; 82557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63756; 94382</t>
+          <t>62384; 95460</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23556; 46785</t>
+          <t>27743; 52193</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>39392</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>70052</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6200; 20751</t>
+          <t>6102; 19372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10782; 30751</t>
+          <t>10596; 31028</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24280; 46818</t>
+          <t>24390; 47228</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10751; 45442</t>
+          <t>20344; 42694</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19156; 40267</t>
+          <t>19642; 40457</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23098; 45537</t>
+          <t>23264; 46802</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62956; 98694</t>
+          <t>63889; 98219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26824; 45411</t>
+          <t>30769; 50359</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28617; 53210</t>
+          <t>29367; 53295</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37925; 67593</t>
+          <t>38208; 66793</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93266; 135048</t>
+          <t>93315; 135103</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40626; 87255</t>
+          <t>55607; 86264</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35024</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57261</t>
+          <t>64527</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9090; 25546</t>
+          <t>9555; 25202</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7877; 22934</t>
+          <t>8028; 23508</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23312; 48006</t>
+          <t>23970; 46980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14779; 32624</t>
+          <t>16240; 35943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14927; 33483</t>
+          <t>14567; 32394</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16855; 36421</t>
+          <t>16832; 37983</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75937; 110922</t>
+          <t>75579; 110266</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27347; 43637</t>
+          <t>31447; 50304</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28307; 52422</t>
+          <t>28314; 52777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28886; 52835</t>
+          <t>27536; 51243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106459; 150586</t>
+          <t>108345; 150851</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45797; 70744</t>
+          <t>51765; 79572</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>230594</t>
+          <t>28564</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>242950</t>
+          <t>42812</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7000; 19503</t>
+          <t>6777; 19337</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7660; 22230</t>
+          <t>7666; 22261</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7814; 21953</t>
+          <t>7981; 21865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7585; 19226</t>
+          <t>8398; 22088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15854; 34535</t>
+          <t>16625; 33895</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23540; 44798</t>
+          <t>23406; 44602</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47758; 77703</t>
+          <t>47783; 77495</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35265; 436522</t>
+          <t>21459; 37031</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26185; 49526</t>
+          <t>26295; 49129</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35336; 60918</t>
+          <t>35611; 61057</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>59900; 93227</t>
+          <t>58563; 93440</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44501; 578649</t>
+          <t>33466; 53765</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>43389</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3478; 13377</t>
+          <t>3472; 13768</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6371; 21665</t>
+          <t>6084; 22264</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14805; 31808</t>
+          <t>14244; 30774</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8722; 20553</t>
+          <t>11138; 25225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15082; 35349</t>
+          <t>15023; 33864</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15431; 34774</t>
+          <t>16071; 36196</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51957; 86165</t>
+          <t>52268; 87169</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18410; 31900</t>
+          <t>19945; 34654</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21850; 43948</t>
+          <t>21658; 44860</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>26557; 52480</t>
+          <t>25936; 51241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71352; 110684</t>
+          <t>71398; 109512</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29568; 47746</t>
+          <t>34078; 53916</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>73626; 110999</t>
+          <t>74179; 109749</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>87233; 129412</t>
+          <t>84969; 127591</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>129217; 177646</t>
+          <t>130715; 179509</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>82858; 137277</t>
+          <t>101698; 148500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>132695; 182661</t>
+          <t>129995; 181669</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>150646; 204182</t>
+          <t>153299; 205236</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>351692; 431385</t>
+          <t>352922; 429414</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>161437; 979354</t>
+          <t>157768; 204755</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>217358; 277457</t>
+          <t>215957; 278037</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>250421; 316364</t>
+          <t>246593; 316238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>502869; 592778</t>
+          <t>500698; 595868</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>271451; 1132535</t>
+          <t>272941; 336245</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
